--- a/aln_control/current_rate_control/low_high/scenarios/sc2.xlsx
+++ b/aln_control/current_rate_control/low_high/scenarios/sc2.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Promotion\neurolib\aln_control\current_rate_control\low_high\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Promotion\neurolib\aln_control\current_rate_control\low_high\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7920FA-2842-4BF1-87AC-1672C7E184F9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE8D4B0-8A9C-42BD-B3DA-032E95E65A0B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="node1Zero" sheetId="1" r:id="rId1"/>
+    <sheet name="node1Input" sheetId="3" r:id="rId1"/>
+    <sheet name="node1Zero" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
+  <si>
+    <t>sparsity</t>
+  </si>
+  <si>
+    <t>energy</t>
+  </si>
+  <si>
+    <t>node0 input just becomes weaker and weaker…</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -68,7 +79,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -90,6 +101,12 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -106,7 +123,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
@@ -114,6 +131,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Gut" xfId="1" builtinId="26"/>
@@ -396,398 +419,1948 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BD29BB-8C7C-44C3-A6D1-DF95BB3A3C6E}">
+  <dimension ref="A1:ES65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="14" max="38" width="10.42578125" customWidth="1"/>
+    <col min="15" max="56" width="10.42578125" customWidth="1"/>
+    <col min="66" max="74" width="3.85546875" customWidth="1"/>
+    <col min="76" max="84" width="4.85546875" customWidth="1"/>
+    <col min="85" max="85" width="9.140625" customWidth="1"/>
+    <col min="86" max="94" width="3.85546875" customWidth="1"/>
+    <col min="96" max="104" width="3.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>1000</v>
+      </c>
+      <c r="G1">
+        <f>F1+1000</f>
+        <v>2000</v>
+      </c>
+      <c r="H1">
+        <f t="shared" ref="H1:BS1" si="0">G1+1000</f>
+        <v>3000</v>
+      </c>
+      <c r="I1">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="J1">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="K1">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="L1">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="M1">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="N1">
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="O1">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="P1">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="Q1">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="R1">
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="S1">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="T1">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="U1">
+        <f t="shared" si="0"/>
+        <v>16000</v>
+      </c>
+      <c r="V1">
+        <f t="shared" si="0"/>
+        <v>17000</v>
+      </c>
+      <c r="W1">
+        <f t="shared" si="0"/>
+        <v>18000</v>
+      </c>
+      <c r="X1">
+        <f t="shared" si="0"/>
+        <v>19000</v>
+      </c>
+      <c r="Y1">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+      <c r="Z1">
+        <f t="shared" si="0"/>
+        <v>21000</v>
+      </c>
+      <c r="AA1">
+        <f t="shared" si="0"/>
+        <v>22000</v>
+      </c>
+      <c r="AB1">
+        <f t="shared" si="0"/>
+        <v>23000</v>
+      </c>
+      <c r="AC1">
+        <f t="shared" si="0"/>
+        <v>24000</v>
+      </c>
+      <c r="AD1">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="AE1">
+        <f t="shared" si="0"/>
+        <v>26000</v>
+      </c>
+      <c r="AF1">
+        <f t="shared" si="0"/>
+        <v>27000</v>
+      </c>
+      <c r="AG1">
+        <f t="shared" si="0"/>
+        <v>28000</v>
+      </c>
+      <c r="AH1">
+        <f t="shared" si="0"/>
+        <v>29000</v>
+      </c>
+      <c r="AI1">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="AJ1">
+        <f t="shared" si="0"/>
+        <v>31000</v>
+      </c>
+      <c r="AK1">
+        <f t="shared" si="0"/>
+        <v>32000</v>
+      </c>
+      <c r="AL1">
+        <f t="shared" si="0"/>
+        <v>33000</v>
+      </c>
+      <c r="AM1">
+        <f t="shared" si="0"/>
+        <v>34000</v>
+      </c>
+      <c r="AN1">
+        <f t="shared" si="0"/>
+        <v>35000</v>
+      </c>
+      <c r="AO1">
+        <f t="shared" si="0"/>
+        <v>36000</v>
+      </c>
+      <c r="AP1">
+        <f t="shared" si="0"/>
+        <v>37000</v>
+      </c>
+      <c r="AQ1">
+        <f t="shared" si="0"/>
+        <v>38000</v>
+      </c>
+      <c r="AR1">
+        <f t="shared" si="0"/>
+        <v>39000</v>
+      </c>
+      <c r="AS1">
+        <f t="shared" si="0"/>
+        <v>40000</v>
+      </c>
+      <c r="AT1">
+        <f t="shared" si="0"/>
+        <v>41000</v>
+      </c>
+      <c r="AU1">
+        <f t="shared" si="0"/>
+        <v>42000</v>
+      </c>
+      <c r="AV1">
+        <f t="shared" si="0"/>
+        <v>43000</v>
+      </c>
+      <c r="AW1">
+        <f t="shared" si="0"/>
+        <v>44000</v>
+      </c>
+      <c r="AX1">
+        <f t="shared" si="0"/>
+        <v>45000</v>
+      </c>
+      <c r="AY1">
+        <f t="shared" si="0"/>
+        <v>46000</v>
+      </c>
+      <c r="AZ1">
+        <f t="shared" si="0"/>
+        <v>47000</v>
+      </c>
+      <c r="BA1">
+        <f t="shared" si="0"/>
+        <v>48000</v>
+      </c>
+      <c r="BB1">
+        <f t="shared" si="0"/>
+        <v>49000</v>
+      </c>
+      <c r="BC1">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
+      <c r="BD1">
+        <f t="shared" si="0"/>
+        <v>51000</v>
+      </c>
+      <c r="BE1">
+        <f t="shared" si="0"/>
+        <v>52000</v>
+      </c>
+      <c r="BF1">
+        <f t="shared" si="0"/>
+        <v>53000</v>
+      </c>
+      <c r="BG1">
+        <f t="shared" si="0"/>
+        <v>54000</v>
+      </c>
+      <c r="BH1">
+        <f t="shared" si="0"/>
+        <v>55000</v>
+      </c>
+      <c r="BI1">
+        <f t="shared" si="0"/>
+        <v>56000</v>
+      </c>
+      <c r="BJ1">
+        <f t="shared" si="0"/>
+        <v>57000</v>
+      </c>
+      <c r="BK1">
+        <f t="shared" si="0"/>
+        <v>58000</v>
+      </c>
+      <c r="BL1">
+        <f t="shared" si="0"/>
+        <v>59000</v>
+      </c>
+      <c r="BM1">
+        <f t="shared" si="0"/>
+        <v>60000</v>
+      </c>
+      <c r="BN1">
+        <f t="shared" si="0"/>
+        <v>61000</v>
+      </c>
+      <c r="BO1">
+        <f t="shared" si="0"/>
+        <v>62000</v>
+      </c>
+      <c r="BP1">
+        <f t="shared" si="0"/>
+        <v>63000</v>
+      </c>
+      <c r="BQ1">
+        <f t="shared" si="0"/>
+        <v>64000</v>
+      </c>
+      <c r="BR1">
+        <f t="shared" si="0"/>
+        <v>65000</v>
+      </c>
+      <c r="BS1">
+        <f t="shared" si="0"/>
+        <v>66000</v>
+      </c>
+      <c r="BT1">
+        <f t="shared" ref="BT1:DA1" si="1">BS1+1000</f>
+        <v>67000</v>
+      </c>
+      <c r="BU1">
+        <f t="shared" si="1"/>
+        <v>68000</v>
+      </c>
+      <c r="BV1">
+        <f t="shared" si="1"/>
+        <v>69000</v>
+      </c>
+      <c r="BW1">
+        <f t="shared" si="1"/>
+        <v>70000</v>
+      </c>
+      <c r="BX1">
+        <f t="shared" si="1"/>
+        <v>71000</v>
+      </c>
+      <c r="BY1">
+        <f t="shared" si="1"/>
+        <v>72000</v>
+      </c>
+      <c r="BZ1">
+        <f t="shared" si="1"/>
+        <v>73000</v>
+      </c>
+      <c r="CA1">
+        <f t="shared" si="1"/>
+        <v>74000</v>
+      </c>
+      <c r="CB1">
+        <f t="shared" si="1"/>
+        <v>75000</v>
+      </c>
+      <c r="CC1">
+        <f t="shared" si="1"/>
+        <v>76000</v>
+      </c>
+      <c r="CD1">
+        <f t="shared" si="1"/>
+        <v>77000</v>
+      </c>
+      <c r="CE1">
+        <f t="shared" si="1"/>
+        <v>78000</v>
+      </c>
+      <c r="CF1">
+        <f t="shared" si="1"/>
+        <v>79000</v>
+      </c>
+      <c r="CG1">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+      <c r="CH1">
+        <f t="shared" si="1"/>
+        <v>81000</v>
+      </c>
+      <c r="CI1">
+        <f t="shared" si="1"/>
+        <v>82000</v>
+      </c>
+      <c r="CJ1">
+        <f t="shared" si="1"/>
+        <v>83000</v>
+      </c>
+      <c r="CK1">
+        <f t="shared" si="1"/>
+        <v>84000</v>
+      </c>
+      <c r="CL1">
+        <f t="shared" si="1"/>
+        <v>85000</v>
+      </c>
+      <c r="CM1">
+        <f t="shared" si="1"/>
+        <v>86000</v>
+      </c>
+      <c r="CN1">
+        <f t="shared" si="1"/>
+        <v>87000</v>
+      </c>
+      <c r="CO1">
+        <f t="shared" si="1"/>
+        <v>88000</v>
+      </c>
+      <c r="CP1">
+        <f t="shared" si="1"/>
+        <v>89000</v>
+      </c>
+      <c r="CQ1">
+        <f t="shared" si="1"/>
+        <v>90000</v>
+      </c>
+      <c r="CR1">
+        <f t="shared" si="1"/>
+        <v>91000</v>
+      </c>
+      <c r="CS1">
+        <f t="shared" si="1"/>
+        <v>92000</v>
+      </c>
+      <c r="CT1">
+        <f t="shared" si="1"/>
+        <v>93000</v>
+      </c>
+      <c r="CU1">
+        <f t="shared" si="1"/>
+        <v>94000</v>
+      </c>
+      <c r="CV1">
+        <f t="shared" si="1"/>
+        <v>95000</v>
+      </c>
+      <c r="CW1">
+        <f t="shared" si="1"/>
+        <v>96000</v>
+      </c>
+      <c r="CX1">
+        <f t="shared" si="1"/>
+        <v>97000</v>
+      </c>
+      <c r="CY1">
+        <f t="shared" si="1"/>
+        <v>98000</v>
+      </c>
+      <c r="CZ1">
+        <f t="shared" si="1"/>
+        <v>99000</v>
+      </c>
+      <c r="DA1">
+        <f t="shared" si="1"/>
+        <v>100000</v>
+      </c>
+      <c r="DB1">
+        <f>DA1+10000</f>
+        <v>110000</v>
+      </c>
+      <c r="DC1">
+        <f t="shared" ref="DC1:DJ1" si="2">DB1+10000</f>
+        <v>120000</v>
+      </c>
+      <c r="DD1">
+        <f t="shared" si="2"/>
+        <v>130000</v>
+      </c>
+      <c r="DE1">
+        <f t="shared" si="2"/>
+        <v>140000</v>
+      </c>
+      <c r="DF1">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="DG1">
+        <f t="shared" si="2"/>
+        <v>160000</v>
+      </c>
+      <c r="DH1">
+        <f t="shared" si="2"/>
+        <v>170000</v>
+      </c>
+      <c r="DI1">
+        <f t="shared" si="2"/>
+        <v>180000</v>
+      </c>
+      <c r="DJ1">
+        <f t="shared" si="2"/>
+        <v>190000</v>
+      </c>
+      <c r="DK1">
+        <v>200000</v>
+      </c>
+      <c r="DL1">
+        <f>DK1+10000</f>
+        <v>210000</v>
+      </c>
+      <c r="DM1">
+        <f t="shared" ref="DM1:DS1" si="3">DL1+10000</f>
+        <v>220000</v>
+      </c>
+      <c r="DN1">
+        <f t="shared" si="3"/>
+        <v>230000</v>
+      </c>
+      <c r="DO1">
+        <f t="shared" si="3"/>
+        <v>240000</v>
+      </c>
+      <c r="DP1">
+        <f t="shared" si="3"/>
+        <v>250000</v>
+      </c>
+      <c r="DQ1">
+        <f t="shared" si="3"/>
+        <v>260000</v>
+      </c>
+      <c r="DR1">
+        <f t="shared" si="3"/>
+        <v>270000</v>
+      </c>
+      <c r="DS1">
+        <f t="shared" si="3"/>
+        <v>280000</v>
+      </c>
+      <c r="DT1">
+        <f>DS1+10000</f>
+        <v>290000</v>
+      </c>
+      <c r="DU1">
+        <v>300000</v>
+      </c>
+      <c r="DV1">
+        <v>310000</v>
+      </c>
+      <c r="DW1">
+        <f>DV1+10000</f>
+        <v>320000</v>
+      </c>
+      <c r="DX1">
+        <f t="shared" ref="DX1:ED1" si="4">DW1+10000</f>
+        <v>330000</v>
+      </c>
+      <c r="DY1">
+        <f t="shared" si="4"/>
+        <v>340000</v>
+      </c>
+      <c r="DZ1">
+        <f t="shared" si="4"/>
+        <v>350000</v>
+      </c>
+      <c r="EA1">
+        <f t="shared" si="4"/>
+        <v>360000</v>
+      </c>
+      <c r="EB1">
+        <f t="shared" si="4"/>
+        <v>370000</v>
+      </c>
+      <c r="EC1">
+        <f t="shared" si="4"/>
+        <v>380000</v>
+      </c>
+      <c r="ED1">
+        <f t="shared" si="4"/>
+        <v>390000</v>
+      </c>
+      <c r="EE1">
+        <v>400000</v>
+      </c>
+      <c r="EG1">
+        <v>500000</v>
+      </c>
+      <c r="EI1">
+        <v>600000</v>
+      </c>
+      <c r="EK1">
+        <v>700000</v>
+      </c>
+      <c r="EM1">
+        <v>800000</v>
+      </c>
+      <c r="EO1">
+        <v>900000</v>
+      </c>
+      <c r="EQ1">
+        <v>1000000</v>
+      </c>
+      <c r="ES1" s="8">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" ref="A8:A26" si="5">A9+1000</f>
+        <v>56000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>22830</v>
+      </c>
+    </row>
+    <row r="9" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="5"/>
+        <v>55000</v>
+      </c>
+      <c r="E9" s="5">
+        <v>22426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="5"/>
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="5"/>
+        <v>53000</v>
+      </c>
+      <c r="E11" s="5">
+        <v>21617</v>
+      </c>
+    </row>
+    <row r="12" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="5"/>
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="5"/>
+        <v>51000</v>
+      </c>
+      <c r="E13" s="5">
+        <v>20812</v>
+      </c>
+    </row>
+    <row r="14" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="5"/>
+        <v>50000</v>
+      </c>
+      <c r="E14" s="5">
+        <v>20404</v>
+      </c>
+      <c r="F14" s="3">
+        <v>24252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="5"/>
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:149" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="5"/>
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="5"/>
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="5"/>
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="5"/>
+        <v>45000</v>
+      </c>
+      <c r="F19" s="5">
+        <v>21834</v>
+      </c>
+    </row>
+    <row r="20" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="5"/>
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="5"/>
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="5"/>
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="5"/>
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="5"/>
+        <v>40000</v>
+      </c>
+      <c r="F24" s="5">
+        <v>19417</v>
+      </c>
+      <c r="O24">
+        <v>20007</v>
+      </c>
+      <c r="Y24">
+        <v>20658</v>
+      </c>
+      <c r="AI24">
+        <v>21309</v>
+      </c>
+      <c r="AS24">
+        <v>21964</v>
+      </c>
+      <c r="AT24">
+        <v>22030</v>
+      </c>
+      <c r="AU24">
+        <v>22096</v>
+      </c>
+      <c r="AV24">
+        <v>22159</v>
+      </c>
+      <c r="AW24">
+        <v>22224</v>
+      </c>
+      <c r="AX24">
+        <v>22288</v>
+      </c>
+      <c r="AY24">
+        <v>22352</v>
+      </c>
+      <c r="AZ24">
+        <v>22418</v>
+      </c>
+      <c r="BA24">
+        <v>22470</v>
+      </c>
+      <c r="BB24" s="3">
+        <v>22539</v>
+      </c>
+      <c r="BC24" s="3">
+        <v>22610</v>
+      </c>
+      <c r="CG24" s="3">
+        <v>24562</v>
+      </c>
+    </row>
+    <row r="25" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="5"/>
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="5"/>
+        <v>38000</v>
+      </c>
+      <c r="F26" s="5">
+        <v>18456</v>
+      </c>
+    </row>
+    <row r="27" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f>A28+1000</f>
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f>A28-1000</f>
+        <v>35000</v>
+      </c>
+      <c r="F29">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" ref="A30:A63" si="6">A29-1000</f>
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="6"/>
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:85" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="6"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="6"/>
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="6"/>
+        <v>30000</v>
+      </c>
+      <c r="F34">
+        <v>14578</v>
+      </c>
+      <c r="DA34" s="5">
+        <v>21024</v>
+      </c>
+      <c r="DC34" s="5">
+        <v>22319</v>
+      </c>
+      <c r="DE34" s="3">
+        <v>23626</v>
+      </c>
+      <c r="DG34" s="3">
+        <v>24910</v>
+      </c>
+    </row>
+    <row r="35" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="6"/>
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="6"/>
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="6"/>
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="6"/>
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="6"/>
+        <v>25000</v>
+      </c>
+      <c r="F39">
+        <v>12165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <f t="shared" si="6"/>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <f t="shared" si="6"/>
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f t="shared" si="6"/>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="6"/>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="6"/>
+        <v>20000</v>
+      </c>
+      <c r="DK44" s="3">
+        <v>22652</v>
+      </c>
+      <c r="DM44" s="3">
+        <v>23945</v>
+      </c>
+    </row>
+    <row r="45" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="6"/>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="6"/>
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="6"/>
+        <v>17000</v>
+      </c>
+      <c r="F47" s="5">
+        <v>8296</v>
+      </c>
+    </row>
+    <row r="48" spans="1:117" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="6"/>
+        <v>16000</v>
+      </c>
+      <c r="F48" s="5">
+        <v>7799</v>
+      </c>
+    </row>
+    <row r="49" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="F49" s="7">
+        <v>6200</v>
+      </c>
+      <c r="DK49">
+        <v>20233</v>
+      </c>
+      <c r="DM49">
+        <v>21527</v>
+      </c>
+      <c r="DO49" s="3">
+        <v>22815</v>
+      </c>
+      <c r="DQ49" s="3">
+        <v>24107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <f t="shared" si="6"/>
+        <v>14000</v>
+      </c>
+      <c r="F50" s="7">
+        <v>5793</v>
+      </c>
+    </row>
+    <row r="51" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <f t="shared" si="6"/>
+        <v>13000</v>
+      </c>
+      <c r="F51" s="7">
+        <v>5385</v>
+      </c>
+    </row>
+    <row r="52" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <f t="shared" si="6"/>
+        <v>12000</v>
+      </c>
+      <c r="F52" s="5">
+        <v>5863</v>
+      </c>
+    </row>
+    <row r="53" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <f t="shared" si="6"/>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <f t="shared" si="6"/>
+        <v>10000</v>
+      </c>
+      <c r="F54">
+        <v>4910</v>
+      </c>
+      <c r="DK54">
+        <v>17796</v>
+      </c>
+      <c r="DM54">
+        <v>19100</v>
+      </c>
+      <c r="DO54">
+        <v>20377</v>
+      </c>
+      <c r="DQ54">
+        <v>21677</v>
+      </c>
+      <c r="DS54" s="3">
+        <v>22974</v>
+      </c>
+      <c r="DU54" s="3">
+        <v>24243</v>
+      </c>
+    </row>
+    <row r="55" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <f t="shared" si="6"/>
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <f t="shared" si="6"/>
+        <v>8000</v>
+      </c>
+      <c r="F56">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="57" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <f t="shared" si="6"/>
+        <v>7000</v>
+      </c>
+      <c r="F57">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="58" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <f t="shared" si="6"/>
+        <v>6000</v>
+      </c>
+      <c r="F58">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="59" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="F59">
+        <v>2486</v>
+      </c>
+      <c r="DP59">
+        <v>18609</v>
+      </c>
+      <c r="DQ59">
+        <v>19254</v>
+      </c>
+      <c r="DR59">
+        <v>19899</v>
+      </c>
+      <c r="DS59">
+        <v>20545</v>
+      </c>
+      <c r="DT59">
+        <v>21190</v>
+      </c>
+      <c r="DU59">
+        <v>21837</v>
+      </c>
+      <c r="DV59">
+        <v>22482</v>
+      </c>
+      <c r="DW59" s="3">
+        <v>23129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <f t="shared" si="6"/>
+        <v>4000</v>
+      </c>
+      <c r="F60">
+        <v>2003</v>
+      </c>
+      <c r="DW60" s="3">
+        <v>22642</v>
+      </c>
+    </row>
+    <row r="61" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <f t="shared" si="6"/>
+        <v>3000</v>
+      </c>
+      <c r="F61">
+        <v>1519</v>
+      </c>
+      <c r="DU61">
+        <v>20865</v>
+      </c>
+      <c r="DV61">
+        <v>21512</v>
+      </c>
+      <c r="DW61">
+        <v>22158</v>
+      </c>
+      <c r="DX61" s="3">
+        <v>22802</v>
+      </c>
+    </row>
+    <row r="62" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <f t="shared" si="6"/>
+        <v>2000</v>
+      </c>
+      <c r="F62">
+        <v>1035</v>
+      </c>
+      <c r="DU62">
+        <v>20380</v>
+      </c>
+      <c r="DV62">
+        <v>21026</v>
+      </c>
+      <c r="DW62">
+        <v>21672</v>
+      </c>
+      <c r="DX62">
+        <v>22318</v>
+      </c>
+      <c r="DY62" s="3">
+        <v>22963</v>
+      </c>
+    </row>
+    <row r="63" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <f t="shared" si="6"/>
+        <v>1000</v>
+      </c>
+      <c r="F63">
+        <v>550</v>
+      </c>
+      <c r="DU63">
+        <v>19894</v>
+      </c>
+      <c r="DV63">
+        <v>20540</v>
+      </c>
+      <c r="DW63">
+        <v>21186</v>
+      </c>
+      <c r="DX63">
+        <v>21832</v>
+      </c>
+      <c r="DY63">
+        <v>22477</v>
+      </c>
+      <c r="DZ63" s="3">
+        <v>23122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:147" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>0</v>
+      </c>
+      <c r="BC64" s="5">
+        <v>4789</v>
+      </c>
+      <c r="BI64" s="5"/>
+      <c r="BJ64" s="4">
+        <v>3700</v>
+      </c>
+      <c r="BM64">
+        <v>3894</v>
+      </c>
+      <c r="BW64">
+        <v>4542</v>
+      </c>
+      <c r="CG64">
+        <v>5189</v>
+      </c>
+      <c r="CQ64">
+        <v>5836</v>
+      </c>
+      <c r="DA64">
+        <v>6483</v>
+      </c>
+      <c r="DK64">
+        <v>12949</v>
+      </c>
+      <c r="DU64">
+        <v>19408</v>
+      </c>
+      <c r="DV64">
+        <v>20054</v>
+      </c>
+      <c r="DW64">
+        <v>20700</v>
+      </c>
+      <c r="DX64">
+        <v>21346</v>
+      </c>
+      <c r="DY64">
+        <v>21990</v>
+      </c>
+      <c r="DZ64" s="3">
+        <v>22637</v>
+      </c>
+      <c r="EA64" s="3">
+        <v>23282</v>
+      </c>
+      <c r="EB64" s="3">
+        <v>23928</v>
+      </c>
+      <c r="EC64" s="3">
+        <v>24621</v>
+      </c>
+      <c r="ED64" s="3"/>
+      <c r="EE64" s="3">
+        <v>25916</v>
+      </c>
+      <c r="EG64">
+        <v>22493</v>
+      </c>
+      <c r="EI64">
+        <v>22493</v>
+      </c>
+      <c r="EK64">
+        <v>22493</v>
+      </c>
+      <c r="EM64">
+        <v>22493</v>
+      </c>
+      <c r="EO64">
+        <v>22493</v>
+      </c>
+      <c r="EQ64">
+        <v>22493</v>
+      </c>
+    </row>
+    <row r="65" spans="63:63" x14ac:dyDescent="0.25">
+      <c r="BK65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BC62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="55" width="10.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
       <c r="E1">
         <v>1000</v>
       </c>
       <c r="F1">
+        <f>E1+1000</f>
         <v>2000</v>
       </c>
       <c r="G1">
+        <f t="shared" ref="G1:AD1" si="0">F1+1000</f>
         <v>3000</v>
       </c>
       <c r="H1">
+        <f t="shared" si="0"/>
         <v>4000</v>
       </c>
       <c r="I1">
+        <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="J1">
+        <f t="shared" si="0"/>
         <v>6000</v>
       </c>
       <c r="K1">
+        <f t="shared" si="0"/>
         <v>7000</v>
       </c>
       <c r="L1">
+        <f t="shared" si="0"/>
         <v>8000</v>
       </c>
       <c r="M1">
+        <f t="shared" si="0"/>
         <v>9000</v>
       </c>
-      <c r="N1" s="1">
-        <f>10000</f>
+      <c r="N1">
+        <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="O1" s="1">
+      <c r="O1">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="P1">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="Q1">
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="R1">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="S1">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="T1">
+        <f t="shared" si="0"/>
+        <v>16000</v>
+      </c>
+      <c r="U1">
+        <f t="shared" si="0"/>
+        <v>17000</v>
+      </c>
+      <c r="V1">
+        <f t="shared" si="0"/>
+        <v>18000</v>
+      </c>
+      <c r="W1">
+        <f t="shared" si="0"/>
+        <v>19000</v>
+      </c>
+      <c r="X1">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+      <c r="Y1">
+        <f t="shared" si="0"/>
+        <v>21000</v>
+      </c>
+      <c r="Z1">
+        <f t="shared" si="0"/>
+        <v>22000</v>
+      </c>
+      <c r="AA1">
+        <f t="shared" si="0"/>
+        <v>23000</v>
+      </c>
+      <c r="AB1">
+        <f t="shared" si="0"/>
+        <v>24000</v>
+      </c>
+      <c r="AC1">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="AD1">
+        <f t="shared" si="0"/>
+        <v>26000</v>
+      </c>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1">
         <f>N1+5000</f>
         <v>15000</v>
       </c>
-      <c r="P1" s="1">
-        <f t="shared" ref="P1:AL1" si="0">O1+5000</f>
+      <c r="AG1" s="1">
+        <f t="shared" ref="AG1:BC1" si="1">AF1+5000</f>
         <v>20000</v>
       </c>
-      <c r="Q1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AH1" s="1">
+        <f t="shared" si="1"/>
         <v>25000</v>
       </c>
-      <c r="R1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AI1" s="1">
+        <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="S1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AJ1" s="1">
+        <f t="shared" si="1"/>
         <v>35000</v>
       </c>
-      <c r="T1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AK1" s="1">
+        <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="U1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AL1" s="1">
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="V1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AM1" s="1">
+        <f t="shared" si="1"/>
         <v>50000</v>
       </c>
-      <c r="W1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AN1" s="1">
+        <f t="shared" si="1"/>
         <v>55000</v>
       </c>
-      <c r="X1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AO1" s="1">
+        <f t="shared" si="1"/>
         <v>60000</v>
       </c>
-      <c r="Y1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AP1" s="1">
+        <f t="shared" si="1"/>
         <v>65000</v>
       </c>
-      <c r="Z1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AQ1" s="1">
+        <f t="shared" si="1"/>
         <v>70000</v>
       </c>
-      <c r="AA1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AR1" s="1">
+        <f t="shared" si="1"/>
         <v>75000</v>
       </c>
-      <c r="AB1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AS1" s="1">
+        <f t="shared" si="1"/>
         <v>80000</v>
       </c>
-      <c r="AC1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AT1" s="1">
+        <f t="shared" si="1"/>
         <v>85000</v>
       </c>
-      <c r="AD1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AU1" s="1">
+        <f t="shared" si="1"/>
         <v>90000</v>
       </c>
-      <c r="AE1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AV1" s="1">
+        <f t="shared" si="1"/>
         <v>95000</v>
       </c>
-      <c r="AF1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AW1" s="1">
+        <f t="shared" si="1"/>
         <v>100000</v>
       </c>
-      <c r="AG1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AX1" s="1">
+        <f t="shared" si="1"/>
         <v>105000</v>
       </c>
-      <c r="AH1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AY1" s="1">
+        <f t="shared" si="1"/>
         <v>110000</v>
       </c>
-      <c r="AI1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AZ1" s="1">
+        <f t="shared" si="1"/>
         <v>115000</v>
       </c>
-      <c r="AJ1" s="1">
-        <f t="shared" si="0"/>
+      <c r="BA1" s="1">
+        <f t="shared" si="1"/>
         <v>120000</v>
       </c>
-      <c r="AK1" s="1">
-        <f t="shared" si="0"/>
+      <c r="BB1" s="1">
+        <f t="shared" si="1"/>
         <v>125000</v>
       </c>
-      <c r="AL1" s="1">
-        <f t="shared" si="0"/>
+      <c r="BC1" s="1">
+        <f t="shared" si="1"/>
         <v>130000</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" ref="A8:A17" si="2">A9+1000</f>
+        <v>55000</v>
+      </c>
+      <c r="E8" s="6">
+        <v>22525</v>
+      </c>
+    </row>
+    <row r="9" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="2"/>
+        <v>54000</v>
+      </c>
+      <c r="E9" s="5">
+        <v>22117</v>
+      </c>
+      <c r="F9" s="5">
+        <v>22200</v>
+      </c>
+      <c r="G9" s="5">
+        <v>22284</v>
+      </c>
+      <c r="H9" s="4">
+        <v>22367</v>
+      </c>
+      <c r="I9" s="4">
+        <v>22450</v>
+      </c>
+      <c r="J9" s="6">
+        <v>22533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="2"/>
+        <v>53000</v>
+      </c>
+      <c r="E10" s="4">
+        <v>21709</v>
+      </c>
+      <c r="J10" s="4">
+        <v>22125</v>
+      </c>
+      <c r="K10" s="5">
+        <v>22209</v>
+      </c>
+      <c r="L10" s="4">
+        <v>22292</v>
+      </c>
+      <c r="M10" s="4">
+        <v>22375</v>
+      </c>
+      <c r="N10" s="4">
+        <v>22458</v>
+      </c>
+      <c r="O10" s="6">
+        <v>22541</v>
+      </c>
+    </row>
+    <row r="11" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="2"/>
+        <v>52000</v>
+      </c>
+      <c r="P11" s="5">
+        <v>22217</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>22300</v>
+      </c>
+      <c r="R11" s="5">
+        <v>22383</v>
+      </c>
+      <c r="S11" s="5">
+        <v>22466</v>
+      </c>
+      <c r="T11" s="3">
+        <v>22549</v>
+      </c>
+    </row>
+    <row r="12" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="2"/>
+        <v>51000</v>
+      </c>
+      <c r="U12" s="5">
+        <v>22225</v>
+      </c>
+      <c r="V12" s="5">
+        <v>22308</v>
+      </c>
+      <c r="W12" s="5">
+        <v>22391</v>
+      </c>
+      <c r="X12" s="5">
+        <v>22474</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>22557</v>
+      </c>
+    </row>
+    <row r="13" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="2"/>
+        <v>50000</v>
+      </c>
+      <c r="E13" s="5">
+        <v>20486</v>
+      </c>
+      <c r="O13" s="4">
+        <v>21318</v>
+      </c>
+      <c r="T13" s="4">
+        <v>21734</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>22150</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>22233</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>22316</v>
+      </c>
+      <c r="AB13" s="5">
+        <v>22399</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>22482</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>22566</v>
+      </c>
+    </row>
+    <row r="14" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="2"/>
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="2"/>
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="2"/>
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="2"/>
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" ref="A18:A25" si="3">A19+1000</f>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="3"/>
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="3"/>
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="3"/>
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="3"/>
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="3"/>
+        <v>40000</v>
+      </c>
+      <c r="E23" s="5">
+        <v>16406</v>
+      </c>
+      <c r="Y23" s="4">
+        <v>18070</v>
+      </c>
+    </row>
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="3"/>
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="3"/>
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f>A27+1000</f>
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>36000</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="AB7" s="2"/>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <f>A7-1000</f>
+      <c r="AS27" s="2"/>
+    </row>
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f>A27-1000</f>
         <v>35000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <f t="shared" ref="A9:A42" si="1">A8-1000</f>
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" ref="A29:A62" si="4">A28-1000</f>
         <v>34000</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E29" s="4">
         <v>13985</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F29" s="4">
         <v>14021</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G29" s="4">
         <v>21146</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="AB9" s="2"/>
-    </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <f t="shared" si="1"/>
+      <c r="AS29" s="2"/>
+    </row>
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="4"/>
         <v>33000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <f t="shared" si="1"/>
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="4"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <f t="shared" si="1"/>
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="4"/>
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <f t="shared" si="1"/>
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="4"/>
         <v>30000</v>
       </c>
-      <c r="AB13" s="2"/>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <f t="shared" si="1"/>
+      <c r="E33" s="4">
+        <v>13325</v>
+      </c>
+      <c r="Y33" s="4">
+        <v>13991</v>
+      </c>
+      <c r="AS33" s="2"/>
+    </row>
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="4"/>
         <v>29000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <f t="shared" si="1"/>
+    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="4"/>
         <v>28000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <f t="shared" si="1"/>
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="4"/>
         <v>27000</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <f t="shared" si="1"/>
+    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="4"/>
         <v>26000</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <f t="shared" si="1"/>
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="4"/>
         <v>25000</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <f t="shared" si="1"/>
+    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="4"/>
         <v>24000</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <f t="shared" si="1"/>
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <f t="shared" si="4"/>
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <f t="shared" si="1"/>
+    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <f t="shared" si="4"/>
         <v>22000</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <f t="shared" si="1"/>
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f t="shared" si="4"/>
         <v>21000</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <f t="shared" si="1"/>
+    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="4"/>
         <v>20000</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <f t="shared" si="1"/>
+      <c r="E43" s="4">
+        <v>8247</v>
+      </c>
+      <c r="Y43" s="4">
+        <v>9911</v>
+      </c>
+    </row>
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="4"/>
         <v>19000</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <f t="shared" si="1"/>
+    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="4"/>
         <v>18000</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <f t="shared" si="1"/>
+    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="4"/>
         <v>17000</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <f t="shared" si="1"/>
+    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="4"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <f t="shared" si="1"/>
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="4"/>
         <v>15000</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <f t="shared" si="1"/>
+    <row r="49" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <f t="shared" si="4"/>
         <v>14000</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <f t="shared" si="1"/>
+    <row r="50" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <f t="shared" si="4"/>
         <v>13000</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <f t="shared" si="1"/>
+    <row r="51" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <f t="shared" si="4"/>
         <v>12000</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <f t="shared" si="1"/>
+    <row r="52" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <f t="shared" si="4"/>
         <v>11000</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <f t="shared" si="1"/>
+    <row r="53" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <f t="shared" si="4"/>
         <v>10000</v>
       </c>
-      <c r="AB33" s="2"/>
-    </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <f t="shared" si="1"/>
+      <c r="E53" s="4">
+        <v>4166</v>
+      </c>
+      <c r="I53" s="4">
+        <v>4499</v>
+      </c>
+      <c r="M53" s="4">
+        <v>4832</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>5165</v>
+      </c>
+      <c r="U53" s="4">
+        <v>5498</v>
+      </c>
+      <c r="Y53" s="4">
+        <v>5831</v>
+      </c>
+      <c r="AS53" s="2"/>
+    </row>
+    <row r="54" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <f t="shared" si="4"/>
         <v>9000</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <f t="shared" si="1"/>
+    <row r="55" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <f t="shared" si="4"/>
         <v>8000</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <f t="shared" si="1"/>
+    <row r="56" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <f t="shared" si="4"/>
         <v>7000</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <f t="shared" si="1"/>
+    <row r="57" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <f t="shared" si="1"/>
+    <row r="58" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <f t="shared" si="4"/>
         <v>5000</v>
       </c>
-    </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <f t="shared" si="1"/>
+      <c r="E58" s="4">
+        <v>2125</v>
+      </c>
+      <c r="G58" s="4">
+        <v>2292</v>
+      </c>
+      <c r="I58" s="4">
+        <v>2458</v>
+      </c>
+      <c r="K58" s="4">
+        <v>2625</v>
+      </c>
+      <c r="M58" s="4">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="59" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <f t="shared" si="4"/>
         <v>4000</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <f t="shared" si="1"/>
+    <row r="60" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <f t="shared" si="1"/>
+    <row r="61" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <f t="shared" si="4"/>
         <v>2000</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <f t="shared" si="1"/>
+    <row r="62" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <f t="shared" si="4"/>
         <v>1000</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="Z42" s="3"/>
-      <c r="AB42" s="3"/>
-      <c r="AD42" s="3"/>
-      <c r="AF42" s="3"/>
-      <c r="AH42" s="3"/>
-      <c r="AJ42" s="2"/>
+      <c r="BA62" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
